--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -810,7 +810,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/masterS-medicalProcedure</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ProcedureCodesMedical_CS</t>
   </si>
   <si>
     <t>Coding.system</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,16 +310,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -445,7 +445,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -473,7 +473,7 @@
 </t>
   </si>
   <si>
-    <t>この手順の外部識別子 / External Identifiers for this procedure</t>
+    <t>このプロシジャー（処置等）の外部identifier / External Identifiers for this procedure</t>
   </si>
   <si>
     <t>これは、ビジネスプロセスによって定義され、リソース自体への直接のURL参照が適切でない場合に参照するために使用される、このProcedureに関連する識別子を記録する。</t>
@@ -482,7 +482,7 @@
     <t>これはビジネス識別子であり、リソース識別子ではない（議論参照）。識別子は1つのリソースインスタンスにのみ表示されることがベストだが、ビジネス上の慣習により、同じ識別子を持つ複数のリソースインスタンスが存在することがあるかもしれない。例えば、複数のPatientとPersonリソースインスタンスが同じ社会保険番号を共有しているかもしれない。</t>
   </si>
   <si>
-    <t>さまざまな参加システムで知られており、サーバー全体で一貫性のある方法で知られている手順を識別できます。 / Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>さまざまな参加システムで知られており、サーバー全体で一貫性のある方法で知られているプロシジャー（処置等）を識別できます。 / Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -525,7 +525,7 @@
     <t>本Procedure全体または一部を遵守する、外部で管理されているプロトコル、ガイドライン、オーダセット、またはその他の定義を指すURL。</t>
   </si>
   <si>
-    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURI識別子である可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURIidentifierである可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
   </si>
   <si>
     <t>Event.instantiatesUri</t>
@@ -602,7 +602,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>手順の状態を指定するコード。 / A code specifying the state of the procedure.</t>
+    <t>プロシジャー（処置等）の状態を指定するコード。 / A code specifying the state of the procedure.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
@@ -655,7 +655,7 @@
     <t>このプロシジャーの分類カテゴリ</t>
   </si>
   <si>
-    <t>検索、並べ替え、表示の手順を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+    <t>検索、並べ替え、表示のプロシジャー（処置等）を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS</t>
@@ -1358,7 +1358,7 @@
 例:自宅での出生、レストランで気管切開など。</t>
   </si>
   <si>
-    <t>記録が保持される可能性が高い場所に手順を結びます。 / Ties a procedure to where the records are likely kept.</t>
+    <t>記録が保持される可能性が高い場所にプロシジャー（処置等）を結びます。 / Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -1518,7 +1518,7 @@
     <t>今後の処置が特別なフォローアップを必要とする場合（例：抜糸）、フォローアップはシンプルなnote として表現してもよいが、より複雑になる可能性もあり、その場合はケアプランリソースを使用することができる。</t>
   </si>
   <si>
-    <t>手順で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
+    <t>プロシジャー（処置等）で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS</t>
@@ -1971,7 +1971,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="69.609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.18359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -1018,7 +1018,7 @@
     <t>Procedure.code.coding:nurse.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.701</t>
+    <t>http://medis.or.jp/CodeSystem/master-nursingAction-16digits</t>
   </si>
   <si>
     <t>Procedure.code.coding:nurse.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -1132,13 +1132,13 @@
 </t>
   </si>
   <si>
-    <t>このプロシジャーの記録が作成された受療の状況</t>
-  </si>
-  <si>
-    <t>プロシジャーが作成または実行された受療の状況、またはこの記録の作成が緊密に関連している受療の状況。</t>
-  </si>
-  <si>
-    <t>これは通常、イベントが発生した出会いの中で行われるが、活動によっては、出会いの公式な終了前または終了後に開始されても、出会いの文脈と結びついている場合がある。</t>
+    <t>このプロシジャーの記録が作成されたEncounterの状況</t>
+  </si>
+  <si>
+    <t>プロシジャーが作成または実行されたEncounterの状況、またはこの記録の作成が緊密に関連している受療の状況。</t>
+  </si>
+  <si>
+    <t>これは通常、イベントが発生したEncounterの中で行われるが、活動によっては、Encounterの公式な終了前または終了後に開始されても、Encounterの文脈と結びついている場合がある。</t>
   </si>
   <si>
     <t>Event.context</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -589,7 +589,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>準備|進行中|not-done |オンホールド|停止|完了|エラーに入った|わからない / preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
+    <t>準備中 | 進行中 | 未完了 | 保留 | 停止 | 完了 | エラー入力 | 不明 / preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
   </si>
   <si>
     <t>プロシージャの状態を指定するコードである。一般的には、進行中または完了した状態になる。【JP Core仕様】http://hl7.org/fhir/us/core/STU3.1/StructureDefinition-us-core-procedure.htmlを参照</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -1947,17 +1947,17 @@
   <dimension ref="A1:AN93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.45703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="227.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1966,26 +1966,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="69.609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.18359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="59.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.7421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="122.22265625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="90.15625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -1431,7 +1431,10 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張extension [procedure-targetbodystructure]（extension-procedure-targetbodystructure.html）を使用する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1971,7 +1974,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.6796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.40625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -10967,9 +10970,11 @@
       <c r="X79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Y79" s="2"/>
+      <c r="Y79" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11005,21 +11010,21 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11045,13 +11050,13 @@
         <v>194</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11081,7 +11086,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11099,7 +11104,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11117,7 +11122,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11128,10 +11133,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11154,16 +11159,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11213,7 +11218,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11231,7 +11236,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11242,10 +11247,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11271,13 +11276,13 @@
         <v>194</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11307,7 +11312,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11325,7 +11330,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11343,7 +11348,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11354,10 +11359,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11380,19 +11385,19 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>380</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11441,7 +11446,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11459,7 +11464,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11470,10 +11475,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11499,10 +11504,10 @@
         <v>194</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11533,7 +11538,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11551,7 +11556,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11569,7 +11574,7 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11580,10 +11585,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11606,16 +11611,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11665,7 +11670,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11680,24 +11685,24 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11723,10 +11728,10 @@
         <v>389</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11777,7 +11782,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11795,7 +11800,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -11806,10 +11811,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11918,10 +11923,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12032,10 +12037,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12148,10 +12153,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12177,10 +12182,10 @@
         <v>194</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12211,7 +12216,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12229,7 +12234,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12247,7 +12252,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12258,10 +12263,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12284,13 +12289,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12341,7 +12346,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>88</v>
@@ -12359,7 +12364,7 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12370,10 +12375,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12396,19 +12401,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12457,7 +12462,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12475,7 +12480,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12486,10 +12491,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12515,13 +12520,13 @@
         <v>194</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12551,7 +12556,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12569,7 +12574,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12587,7 +12592,7 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -364,7 +364,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -500,7 +500,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -538,7 +538,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1434,7 +1434,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1595,7 +1595,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -680,7 +680,7 @@
     <t>行われた具体的な手順。手技の正確な性質がコード化できない場合はテキストを使用する（例：「腹腔鏡下虫垂切除術」）</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供すべきである。</t>
+    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供すべきである。</t>
   </si>
   <si>
     <t>0..1主に叙述(Narative)のみのリソースを説明する。 / 0..1 to account for primarily narrative only resources.</t>
@@ -1272,7 +1272,7 @@
     <t>プロシジャーへの実施者の関与のタイプを区別する。たとえば、外科医、麻酔科医、内視鏡医。</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供するべきである。  
+    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供するべきである。  
  【JP Core仕様】当面利用しない。</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-procedure.xlsx
@@ -1544,7 +1544,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。   
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
